--- a/gte/nodes/HPT/turbine_stage_1_blade_stator_coordinates_foil.xlsx
+++ b/gte/nodes/HPT/turbine_stage_1_blade_stator_coordinates_foil.xlsx
@@ -349,647 +349,647 @@
         <v>0</v>
       </c>
       <c r="B1">
-        <v>-7.5479344121848443E-18</v>
+        <v>0</v>
       </c>
     </row>
     <row r="2" spans="1:2">
       <c r="A2">
-        <v>0.0016996437303066305</v>
+        <v>0.0016992773431233014</v>
       </c>
       <c r="B2">
-        <v>0.0034819219694949238</v>
+        <v>0.0034808949017546219</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3">
-        <v>0.003399287460613261</v>
+        <v>0.0033985546862466028</v>
       </c>
       <c r="B3">
-        <v>0.0054474284540267943</v>
+        <v>0.005445736013850744</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4">
-        <v>0.005098931190919892</v>
+        <v>0.005097832029369905</v>
       </c>
       <c r="B4">
-        <v>0.0070768979818683665</v>
+        <v>0.0070746412560979306</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5">
-        <v>0.0067985749212265221</v>
+        <v>0.0067971093724932055</v>
       </c>
       <c r="B5">
-        <v>0.008481021406424951</v>
+        <v>0.008478274216156283</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6">
-        <v>0.0084982186515331522</v>
+        <v>0.0084963867156165069</v>
       </c>
       <c r="B6">
-        <v>0.0097149260966221049</v>
+        <v>0.00971174643066785</v>
       </c>
     </row>
     <row r="7" spans="1:2">
       <c r="A7">
-        <v>0.010197862381839784</v>
+        <v>0.01019566405873981</v>
       </c>
       <c r="B7">
-        <v>0.010799318011759323</v>
+        <v>0.010795757547084955</v>
       </c>
     </row>
     <row r="8" spans="1:2">
       <c r="A8">
-        <v>0.011897506112146414</v>
+        <v>0.011894941401863111</v>
       </c>
       <c r="B8">
-        <v>0.011762002167472066</v>
+        <v>0.011758103113145173</v>
       </c>
     </row>
     <row r="9" spans="1:2">
       <c r="A9">
-        <v>0.013597149842453044</v>
+        <v>0.013594218744986411</v>
       </c>
       <c r="B9">
-        <v>0.012611883884145053</v>
+        <v>0.01260768524843706</v>
       </c>
     </row>
     <row r="10" spans="1:2">
       <c r="A10">
-        <v>0.015296793572759674</v>
+        <v>0.015293496088109712</v>
       </c>
       <c r="B10">
-        <v>0.01335671996926893</v>
+        <v>0.013352257861607127</v>
       </c>
     </row>
     <row r="11" spans="1:2">
       <c r="A11">
-        <v>0.016996437303066304</v>
+        <v>0.016992773431233014</v>
       </c>
       <c r="B11">
-        <v>0.014003398151060229</v>
+        <v>0.013998706058482432</v>
       </c>
     </row>
     <row r="12" spans="1:2">
       <c r="A12">
-        <v>0.018696081033372936</v>
+        <v>0.018692050774356317</v>
       </c>
       <c r="B12">
-        <v>0.014558108410664874</v>
+        <v>0.014553217456599864</v>
       </c>
     </row>
     <row r="13" spans="1:2">
       <c r="A13">
-        <v>0.020395724763679568</v>
+        <v>0.02039132811747962</v>
       </c>
       <c r="B13">
-        <v>0.01502645121755068</v>
+        <v>0.015021390404822976</v>
       </c>
     </row>
     <row r="14" spans="1:2">
       <c r="A14">
-        <v>0.022095368493986196</v>
+        <v>0.02209060546060292</v>
       </c>
       <c r="B14">
-        <v>0.015413509988431271</v>
+        <v>0.015408306425725262</v>
       </c>
     </row>
     <row r="15" spans="1:2">
       <c r="A15">
-        <v>0.023795012224292828</v>
+        <v>0.023789882803726223</v>
       </c>
       <c r="B15">
-        <v>0.01572390460116365</v>
+        <v>0.015718583711110175</v>
       </c>
     </row>
     <row r="16" spans="1:2">
       <c r="A16">
-        <v>0.025494655954599457</v>
+        <v>0.025489160146849522</v>
       </c>
       <c r="B16">
-        <v>0.015961836466076323</v>
+        <v>0.015956422172732531</v>
       </c>
     </row>
     <row r="17" spans="1:2">
       <c r="A17">
-        <v>0.027194299684906088</v>
+        <v>0.027188437489972822</v>
       </c>
       <c r="B17">
-        <v>0.016131131800279724</v>
+        <v>0.016125646693564578</v>
       </c>
     </row>
     <row r="18" spans="1:2">
       <c r="A18">
-        <v>0.02889394341521272</v>
+        <v>0.028887714833096125</v>
       </c>
       <c r="B18">
-        <v>0.016235287406259191</v>
+        <v>0.016229752880605287</v>
       </c>
     </row>
     <row r="19" spans="1:2">
       <c r="A19">
-        <v>0.030593587145519349</v>
+        <v>0.030586992176219425</v>
       </c>
       <c r="B19">
-        <v>0.016255800823513359</v>
+        <v>0.016250244325099521</v>
       </c>
     </row>
     <row r="20" spans="1:2">
       <c r="A20">
-        <v>0.03229323087582598</v>
+        <v>0.032286269519342728</v>
       </c>
       <c r="B20">
-        <v>0.016213615467260578</v>
+        <v>0.016208057599299</v>
       </c>
     </row>
     <row r="21" spans="1:2">
       <c r="A21">
-        <v>0.033992874606132609</v>
+        <v>0.033985546862466028</v>
       </c>
       <c r="B21">
-        <v>0.016112495800351911</v>
+        <v>0.01610695597897794</v>
       </c>
     </row>
     <row r="22" spans="1:2">
       <c r="A22">
-        <v>0.035692518336439244</v>
+        <v>0.035684824205589327</v>
       </c>
       <c r="B22">
-        <v>0.015954931175805653</v>
+        <v>0.015949428046386445</v>
       </c>
     </row>
     <row r="23" spans="1:2">
       <c r="A23">
-        <v>0.037392162066745872</v>
+        <v>0.037384101548712634</v>
       </c>
       <c r="B23">
-        <v>0.015721789050567953</v>
+        <v>0.015716347725383</v>
       </c>
     </row>
     <row r="24" spans="1:2">
       <c r="A24">
-        <v>0.039091805797052508</v>
+        <v>0.039083378891835933</v>
       </c>
       <c r="B24">
-        <v>0.015424561170689136</v>
+        <v>0.015419203163085192</v>
       </c>
     </row>
     <row r="25" spans="1:2">
       <c r="A25">
-        <v>0.040791449527359136</v>
+        <v>0.04078265623495924</v>
       </c>
       <c r="B25">
-        <v>0.01507433352262233</v>
+        <v>0.015069076771330041</v>
       </c>
     </row>
     <row r="26" spans="1:2">
       <c r="A26">
-        <v>0.042491093257665757</v>
+        <v>0.042481933578082533</v>
       </c>
       <c r="B26">
-        <v>0.014668767825262144</v>
+        <v>0.01466363116513739</v>
       </c>
     </row>
     <row r="27" spans="1:2">
       <c r="A27">
-        <v>0.044190736987972393</v>
+        <v>0.044181210921205839</v>
       </c>
       <c r="B27">
-        <v>0.014178762307020913</v>
+        <v>0.014173774990310303</v>
       </c>
     </row>
     <row r="28" spans="1:2">
       <c r="A28">
-        <v>0.045890380718279028</v>
+        <v>0.045880488264329139</v>
       </c>
       <c r="B28">
-        <v>0.013637151349257243</v>
+        <v>0.013632331617142092</v>
       </c>
     </row>
     <row r="29" spans="1:2">
       <c r="A29">
-        <v>0.047590024448585656</v>
+        <v>0.047579765607452446</v>
       </c>
       <c r="B29">
-        <v>0.013045409806481747</v>
+        <v>0.013040775471809516</v>
       </c>
     </row>
     <row r="30" spans="1:2">
       <c r="A30">
-        <v>0.049289668178892292</v>
+        <v>0.049279042950575745</v>
       </c>
       <c r="B30">
-        <v>0.012365936750454332</v>
+        <v>0.012361519714056015</v>
       </c>
     </row>
     <row r="31" spans="1:2">
       <c r="A31">
-        <v>0.050989311909198913</v>
+        <v>0.050978320293699045</v>
       </c>
       <c r="B31">
-        <v>0.01162759284035361</v>
+        <v>0.011623415196907348</v>
       </c>
     </row>
     <row r="32" spans="1:2">
       <c r="A32">
-        <v>0.052688955639505548</v>
+        <v>0.052677597636822344</v>
       </c>
       <c r="B32">
-        <v>0.010838090260538258</v>
+        <v>0.010834171378489695</v>
       </c>
     </row>
     <row r="33" spans="1:2">
       <c r="A33">
-        <v>0.054388599369812177</v>
+        <v>0.054376874979945644</v>
       </c>
       <c r="B33">
-        <v>0.0099570815806846059</v>
+        <v>0.00995345710845983</v>
       </c>
     </row>
     <row r="34" spans="1:2">
       <c r="A34">
-        <v>0.056088243100118812</v>
+        <v>0.056076152323068951</v>
       </c>
       <c r="B34">
-        <v>0.0090085933345202557</v>
+        <v>0.0090052907338736832</v>
       </c>
     </row>
     <row r="35" spans="1:2">
       <c r="A35">
-        <v>0.05778788683042544</v>
+        <v>0.05777542966619225</v>
       </c>
       <c r="B35">
-        <v>0.0080055279931044235</v>
+        <v>0.0080025697394905653</v>
       </c>
     </row>
     <row r="36" spans="1:2">
       <c r="A36">
-        <v>0.059487530560732069</v>
+        <v>0.05947470700931555</v>
       </c>
       <c r="B36">
-        <v>0.0068974396345324821</v>
+        <v>0.0068948707003450042</v>
       </c>
     </row>
     <row r="37" spans="1:2">
       <c r="A37">
-        <v>0.0611871742910387</v>
+        <v>0.06117398435243885</v>
       </c>
       <c r="B37">
-        <v>0.005714583327294926</v>
+        <v>0.0057124376831210388</v>
       </c>
     </row>
     <row r="38" spans="1:2">
       <c r="A38">
-        <v>0.062886818021345325</v>
+        <v>0.062873261695562149</v>
       </c>
       <c r="B38">
-        <v>0.0044705388344550767</v>
+        <v>0.0044688445619296422</v>
       </c>
     </row>
     <row r="39" spans="1:2">
       <c r="A39">
-        <v>0.064586461751651961</v>
+        <v>0.064572539038685456</v>
       </c>
       <c r="B39">
-        <v>0.003095466696559579</v>
+        <v>0.0030942875806971555</v>
       </c>
     </row>
     <row r="40" spans="1:2">
       <c r="A40">
-        <v>0.0662861054819586</v>
+        <v>0.066271816381808762</v>
       </c>
       <c r="B40">
-        <v>0.0017203945586640817</v>
+        <v>0.0017197305994646685</v>
       </c>
     </row>
     <row r="41" spans="1:2">
       <c r="A41">
-        <v>0.067985749212265217</v>
+        <v>0.067971093724932055</v>
       </c>
       <c r="B41">
-        <v>0.0003453224207685899</v>
+        <v>0.00034517361823218696</v>
       </c>
     </row>
     <row r="42" spans="1:2">
       <c r="A42">
-        <v>0.067985749212265217</v>
+        <v>0.067971093724932055</v>
       </c>
       <c r="B42">
-        <v>9.1060514363934392E-05</v>
+        <v>9.0966522316373092E-05</v>
       </c>
     </row>
     <row r="43" spans="1:2">
       <c r="A43">
-        <v>0.0662861054819586</v>
+        <v>0.066271816381808762</v>
       </c>
       <c r="B43">
-        <v>0.00090988924159719959</v>
+        <v>0.000909400000637202</v>
       </c>
     </row>
     <row r="44" spans="1:2">
       <c r="A44">
-        <v>0.064586461751651961</v>
+        <v>0.064572539038685456</v>
       </c>
       <c r="B44">
-        <v>0.0017287179688304686</v>
+        <v>0.0017278334789580347</v>
       </c>
     </row>
     <row r="45" spans="1:2">
       <c r="A45">
-        <v>0.062886818021345325</v>
+        <v>0.062873261695562149</v>
       </c>
       <c r="B45">
-        <v>0.0025475466960637378</v>
+        <v>0.0025462669572788674</v>
       </c>
     </row>
     <row r="46" spans="1:2">
       <c r="A46">
-        <v>0.0611871742910387</v>
+        <v>0.06117398435243885</v>
       </c>
       <c r="B46">
-        <v>0.003258239048184881</v>
+        <v>0.0032566229108986211</v>
       </c>
     </row>
     <row r="47" spans="1:2">
       <c r="A47">
-        <v>0.059487530560732069</v>
+        <v>0.05947470700931555</v>
       </c>
       <c r="B47">
-        <v>0.0039187487209285153</v>
+        <v>0.0039168218943512285</v>
       </c>
     </row>
     <row r="48" spans="1:2">
       <c r="A48">
-        <v>0.05778788683042544</v>
+        <v>0.05777542966619225</v>
       </c>
       <c r="B48">
-        <v>0.0045180019947245213</v>
+        <v>0.0045157955367985184</v>
       </c>
     </row>
     <row r="49" spans="1:2">
       <c r="A49">
-        <v>0.056088243100118812</v>
+        <v>0.056076152323068951</v>
       </c>
       <c r="B49">
-        <v>0.0050318904571119965</v>
+        <v>0.0050294451025695392</v>
       </c>
     </row>
     <row r="50" spans="1:2">
       <c r="A50">
-        <v>0.054388599369812177</v>
+        <v>0.054376874979945644</v>
       </c>
       <c r="B50">
-        <v>0.0055017406570293656</v>
+        <v>0.0054990766094998849</v>
       </c>
     </row>
     <row r="51" spans="1:2">
       <c r="A51">
-        <v>0.052688955639505548</v>
+        <v>0.052677597636822344</v>
       </c>
       <c r="B51">
-        <v>0.0059172596314066069</v>
+        <v>0.0059144015182954974</v>
       </c>
     </row>
     <row r="52" spans="1:2">
       <c r="A52">
-        <v>0.050989311909198913</v>
+        <v>0.050978320293699045</v>
       </c>
       <c r="B52">
-        <v>0.0062599724461748132</v>
+        <v>0.0062569518848171893</v>
       </c>
     </row>
     <row r="53" spans="1:2">
       <c r="A53">
-        <v>0.049289668178892292</v>
+        <v>0.049279042950575745</v>
       </c>
       <c r="B53">
-        <v>0.0065624477108060424</v>
+        <v>0.0065592817154140268</v>
       </c>
     </row>
     <row r="54" spans="1:2">
       <c r="A54">
-        <v>0.047590024448585656</v>
+        <v>0.047579765607452446</v>
       </c>
       <c r="B54">
-        <v>0.0068187803647302737</v>
+        <v>0.0068154882861921487</v>
       </c>
     </row>
     <row r="55" spans="1:2">
       <c r="A55">
-        <v>0.045890380718279028</v>
+        <v>0.045880488264329139</v>
       </c>
       <c r="B55">
-        <v>0.0070076250899541656</v>
+        <v>0.0070042344652511386</v>
       </c>
     </row>
     <row r="56" spans="1:2">
       <c r="A56">
-        <v>0.044190736987972393</v>
+        <v>0.044181210921205839</v>
       </c>
       <c r="B56">
-        <v>0.0071586667803055877</v>
+        <v>0.0071551927648715171</v>
       </c>
     </row>
     <row r="57" spans="1:2">
       <c r="A57">
-        <v>0.042491093257665757</v>
+        <v>0.042481933578082533</v>
       </c>
       <c r="B57">
-        <v>0.0072709947780857966</v>
+        <v>0.0072674528340661475</v>
       </c>
     </row>
     <row r="58" spans="1:2">
       <c r="A58">
-        <v>0.040791449527359136</v>
+        <v>0.04078265623495924</v>
       </c>
       <c r="B58">
-        <v>0.0073215542658121363</v>
+        <v>0.0073179687582659494</v>
       </c>
     </row>
     <row r="59" spans="1:2">
       <c r="A59">
-        <v>0.039091805797052508</v>
+        <v>0.039083378891835933</v>
       </c>
       <c r="B59">
-        <v>0.0073329138721345026</v>
+        <v>0.0073293001570604276</v>
       </c>
     </row>
     <row r="60" spans="1:2">
       <c r="A60">
-        <v>0.037392162066745872</v>
+        <v>0.037384101548712634</v>
       </c>
       <c r="B60">
-        <v>0.0073072832302911893</v>
+        <v>0.0073036557952948821</v>
       </c>
     </row>
     <row r="61" spans="1:2">
       <c r="A61">
-        <v>0.035692518336439244</v>
+        <v>0.035684824205589327</v>
       </c>
       <c r="B61">
-        <v>0.0072379052422061321</v>
+        <v>0.0072342812163436682</v>
       </c>
     </row>
     <row r="62" spans="1:2">
       <c r="A62">
-        <v>0.033992874606132609</v>
+        <v>0.033985546862466028</v>
       </c>
       <c r="B62">
-        <v>0.0071190544189580329</v>
+        <v>0.0071154532872031934</v>
       </c>
     </row>
     <row r="63" spans="1:2">
       <c r="A63">
-        <v>0.03229323087582598</v>
+        <v>0.032286269519342728</v>
       </c>
       <c r="B63">
-        <v>0.0069646723715445337</v>
+        <v>0.0069611082709526585</v>
       </c>
     </row>
     <row r="64" spans="1:2">
       <c r="A64">
-        <v>0.030593587145519349</v>
+        <v>0.030586992176219425</v>
       </c>
       <c r="B64">
-        <v>0.0067741692015367361</v>
+        <v>0.0067706566304715481</v>
       </c>
     </row>
     <row r="65" spans="1:2">
       <c r="A65">
-        <v>0.02889394341521272</v>
+        <v>0.028887714833096125</v>
       </c>
       <c r="B65">
-        <v>0.0065464915274407037</v>
+        <v>0.0065430455869229642</v>
       </c>
     </row>
     <row r="66" spans="1:2">
       <c r="A66">
-        <v>0.027194299684906088</v>
+        <v>0.027188437489972822</v>
       </c>
       <c r="B66">
-        <v>0.0062719844864476508</v>
+        <v>0.0062686246870248073</v>
       </c>
     </row>
     <row r="67" spans="1:2">
       <c r="A67">
-        <v>0.025494655954599457</v>
+        <v>0.025489160146849522</v>
       </c>
       <c r="B67">
-        <v>0.0059631952951369879</v>
+        <v>0.0059599363793646342</v>
       </c>
     </row>
     <row r="68" spans="1:2">
       <c r="A68">
-        <v>0.023795012224292828</v>
+        <v>0.023789882803726223</v>
       </c>
       <c r="B68">
-        <v>0.0056199882406230747</v>
+        <v>0.0056168454220029973</v>
       </c>
     </row>
     <row r="69" spans="1:2">
       <c r="A69">
-        <v>0.022095368493986196</v>
+        <v>0.02209060546060292</v>
       </c>
       <c r="B69">
-        <v>0.0052424507504102271</v>
+        <v>0.0052394397329295767</v>
       </c>
     </row>
     <row r="70" spans="1:2">
       <c r="A70">
-        <v>0.020395724763679568</v>
+        <v>0.02039132811747962</v>
       </c>
       <c r="B70">
-        <v>0.0048309350270308981</v>
+        <v>0.0048280720316416295</v>
       </c>
     </row>
     <row r="71" spans="1:2">
       <c r="A71">
-        <v>0.018696081033372936</v>
+        <v>0.018692050774356317</v>
       </c>
       <c r="B71">
-        <v>0.0043861183644629074</v>
+        <v>0.0043834201562748271</v>
       </c>
     </row>
     <row r="72" spans="1:2">
       <c r="A72">
-        <v>0.016996437303066304</v>
+        <v>0.016992773431233014</v>
       </c>
       <c r="B72">
-        <v>0.0039090893332858548</v>
+        <v>0.00390657324107181</v>
       </c>
     </row>
     <row r="73" spans="1:2">
       <c r="A73">
-        <v>0.015296793572759674</v>
+        <v>0.015293496088109712</v>
       </c>
       <c r="B73">
-        <v>0.0034014704561000555</v>
+        <v>0.0033991543721980733</v>
       </c>
     </row>
     <row r="74" spans="1:2">
       <c r="A74">
-        <v>0.013597149842453044</v>
+        <v>0.013594218744986411</v>
       </c>
       <c r="B74">
-        <v>0.0028655927496587276</v>
+        <v>0.0028634950931694931</v>
       </c>
     </row>
     <row r="75" spans="1:2">
       <c r="A75">
-        <v>0.011897506112146414</v>
+        <v>0.011894941401863111</v>
       </c>
       <c r="B75">
-        <v>0.0023047444430675736</v>
+        <v>0.00230288406188016</v>
       </c>
     </row>
     <row r="76" spans="1:2">
       <c r="A76">
-        <v>0.010197862381839784</v>
+        <v>0.01019566405873981</v>
       </c>
       <c r="B76">
-        <v>0.0017235268139964841</v>
+        <v>0.0017219227908481466</v>
       </c>
     </row>
     <row r="77" spans="1:2">
       <c r="A77">
-        <v>0.0084982186515331522</v>
+        <v>0.0084963867156165069</v>
       </c>
       <c r="B77">
-        <v>0.0011283672214373482</v>
+        <v>0.0011270385346410616</v>
       </c>
     </row>
     <row r="78" spans="1:2">
       <c r="A78">
-        <v>0.0067985749212265221</v>
+        <v>0.0067971093724932055</v>
       </c>
       <c r="B78">
-        <v>0.00052933319444710251</v>
+        <v>0.00052830012614102492</v>
       </c>
     </row>
     <row r="79" spans="1:2">
       <c r="A79">
-        <v>0.005098931190919892</v>
+        <v>0.005097832029369905</v>
       </c>
       <c r="B79">
-        <v>-5.5105529771081816E-05</v>
+        <v>-5.5824830590906132E-05</v>
       </c>
     </row>
     <row r="80" spans="1:2">
       <c r="A80">
-        <v>0.003399287460613261</v>
+        <v>0.0033985546862466028</v>
       </c>
       <c r="B80">
-        <v>-0.00058362388142422291</v>
+        <v>-0.00058401622544583065</v>
       </c>
     </row>
     <row r="81" spans="1:2">
       <c r="A81">
-        <v>0.0016996437303066305</v>
+        <v>0.0016992773431233014</v>
       </c>
       <c r="B81">
-        <v>-0.00095239285724307225</v>
+        <v>-0.00095246403282174508</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -997,7 +997,7 @@
         <v>0</v>
       </c>
       <c r="B82">
-        <v>-7.5479344121848443E-18</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1015,647 +1015,647 @@
         <v>0</v>
       </c>
       <c r="B1">
-        <v>-7.5479344121848443E-18</v>
+        <v>0</v>
       </c>
     </row>
     <row r="2" spans="1:2">
       <c r="A2">
-        <v>0.0016996437303066305</v>
+        <v>0.0016992773431233014</v>
       </c>
       <c r="B2">
-        <v>0.0034819219694949238</v>
+        <v>0.0034808949017546219</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3">
-        <v>0.003399287460613261</v>
+        <v>0.0033985546862466028</v>
       </c>
       <c r="B3">
-        <v>0.0054474284540267943</v>
+        <v>0.005445736013850744</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4">
-        <v>0.005098931190919892</v>
+        <v>0.005097832029369905</v>
       </c>
       <c r="B4">
-        <v>0.0070768979818683665</v>
+        <v>0.0070746412560979306</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5">
-        <v>0.0067985749212265221</v>
+        <v>0.0067971093724932055</v>
       </c>
       <c r="B5">
-        <v>0.008481021406424951</v>
+        <v>0.008478274216156283</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6">
-        <v>0.0084982186515331522</v>
+        <v>0.0084963867156165069</v>
       </c>
       <c r="B6">
-        <v>0.0097149260966221049</v>
+        <v>0.00971174643066785</v>
       </c>
     </row>
     <row r="7" spans="1:2">
       <c r="A7">
-        <v>0.010197862381839784</v>
+        <v>0.01019566405873981</v>
       </c>
       <c r="B7">
-        <v>0.010799318011759323</v>
+        <v>0.010795757547084955</v>
       </c>
     </row>
     <row r="8" spans="1:2">
       <c r="A8">
-        <v>0.011897506112146414</v>
+        <v>0.011894941401863111</v>
       </c>
       <c r="B8">
-        <v>0.011762002167472066</v>
+        <v>0.011758103113145173</v>
       </c>
     </row>
     <row r="9" spans="1:2">
       <c r="A9">
-        <v>0.013597149842453044</v>
+        <v>0.013594218744986411</v>
       </c>
       <c r="B9">
-        <v>0.012611883884145053</v>
+        <v>0.01260768524843706</v>
       </c>
     </row>
     <row r="10" spans="1:2">
       <c r="A10">
-        <v>0.015296793572759674</v>
+        <v>0.015293496088109712</v>
       </c>
       <c r="B10">
-        <v>0.01335671996926893</v>
+        <v>0.013352257861607127</v>
       </c>
     </row>
     <row r="11" spans="1:2">
       <c r="A11">
-        <v>0.016996437303066304</v>
+        <v>0.016992773431233014</v>
       </c>
       <c r="B11">
-        <v>0.014003398151060229</v>
+        <v>0.013998706058482432</v>
       </c>
     </row>
     <row r="12" spans="1:2">
       <c r="A12">
-        <v>0.018696081033372936</v>
+        <v>0.018692050774356317</v>
       </c>
       <c r="B12">
-        <v>0.014558108410664874</v>
+        <v>0.014553217456599864</v>
       </c>
     </row>
     <row r="13" spans="1:2">
       <c r="A13">
-        <v>0.020395724763679568</v>
+        <v>0.02039132811747962</v>
       </c>
       <c r="B13">
-        <v>0.01502645121755068</v>
+        <v>0.015021390404822976</v>
       </c>
     </row>
     <row r="14" spans="1:2">
       <c r="A14">
-        <v>0.022095368493986196</v>
+        <v>0.02209060546060292</v>
       </c>
       <c r="B14">
-        <v>0.015413509988431271</v>
+        <v>0.015408306425725262</v>
       </c>
     </row>
     <row r="15" spans="1:2">
       <c r="A15">
-        <v>0.023795012224292828</v>
+        <v>0.023789882803726223</v>
       </c>
       <c r="B15">
-        <v>0.01572390460116365</v>
+        <v>0.015718583711110175</v>
       </c>
     </row>
     <row r="16" spans="1:2">
       <c r="A16">
-        <v>0.025494655954599457</v>
+        <v>0.025489160146849522</v>
       </c>
       <c r="B16">
-        <v>0.015961836466076323</v>
+        <v>0.015956422172732531</v>
       </c>
     </row>
     <row r="17" spans="1:2">
       <c r="A17">
-        <v>0.027194299684906088</v>
+        <v>0.027188437489972822</v>
       </c>
       <c r="B17">
-        <v>0.016131131800279724</v>
+        <v>0.016125646693564578</v>
       </c>
     </row>
     <row r="18" spans="1:2">
       <c r="A18">
-        <v>0.02889394341521272</v>
+        <v>0.028887714833096125</v>
       </c>
       <c r="B18">
-        <v>0.016235287406259191</v>
+        <v>0.016229752880605287</v>
       </c>
     </row>
     <row r="19" spans="1:2">
       <c r="A19">
-        <v>0.030593587145519349</v>
+        <v>0.030586992176219425</v>
       </c>
       <c r="B19">
-        <v>0.016255800823513359</v>
+        <v>0.016250244325099521</v>
       </c>
     </row>
     <row r="20" spans="1:2">
       <c r="A20">
-        <v>0.03229323087582598</v>
+        <v>0.032286269519342728</v>
       </c>
       <c r="B20">
-        <v>0.016213615467260578</v>
+        <v>0.016208057599299</v>
       </c>
     </row>
     <row r="21" spans="1:2">
       <c r="A21">
-        <v>0.033992874606132609</v>
+        <v>0.033985546862466028</v>
       </c>
       <c r="B21">
-        <v>0.016112495800351911</v>
+        <v>0.01610695597897794</v>
       </c>
     </row>
     <row r="22" spans="1:2">
       <c r="A22">
-        <v>0.035692518336439244</v>
+        <v>0.035684824205589327</v>
       </c>
       <c r="B22">
-        <v>0.015954931175805653</v>
+        <v>0.015949428046386445</v>
       </c>
     </row>
     <row r="23" spans="1:2">
       <c r="A23">
-        <v>0.037392162066745872</v>
+        <v>0.037384101548712634</v>
       </c>
       <c r="B23">
-        <v>0.015721789050567953</v>
+        <v>0.015716347725383</v>
       </c>
     </row>
     <row r="24" spans="1:2">
       <c r="A24">
-        <v>0.039091805797052508</v>
+        <v>0.039083378891835933</v>
       </c>
       <c r="B24">
-        <v>0.015424561170689136</v>
+        <v>0.015419203163085192</v>
       </c>
     </row>
     <row r="25" spans="1:2">
       <c r="A25">
-        <v>0.040791449527359136</v>
+        <v>0.04078265623495924</v>
       </c>
       <c r="B25">
-        <v>0.01507433352262233</v>
+        <v>0.015069076771330041</v>
       </c>
     </row>
     <row r="26" spans="1:2">
       <c r="A26">
-        <v>0.042491093257665757</v>
+        <v>0.042481933578082533</v>
       </c>
       <c r="B26">
-        <v>0.014668767825262144</v>
+        <v>0.01466363116513739</v>
       </c>
     </row>
     <row r="27" spans="1:2">
       <c r="A27">
-        <v>0.044190736987972393</v>
+        <v>0.044181210921205839</v>
       </c>
       <c r="B27">
-        <v>0.014178762307020913</v>
+        <v>0.014173774990310303</v>
       </c>
     </row>
     <row r="28" spans="1:2">
       <c r="A28">
-        <v>0.045890380718279028</v>
+        <v>0.045880488264329139</v>
       </c>
       <c r="B28">
-        <v>0.013637151349257243</v>
+        <v>0.013632331617142092</v>
       </c>
     </row>
     <row r="29" spans="1:2">
       <c r="A29">
-        <v>0.047590024448585656</v>
+        <v>0.047579765607452446</v>
       </c>
       <c r="B29">
-        <v>0.013045409806481747</v>
+        <v>0.013040775471809516</v>
       </c>
     </row>
     <row r="30" spans="1:2">
       <c r="A30">
-        <v>0.049289668178892292</v>
+        <v>0.049279042950575745</v>
       </c>
       <c r="B30">
-        <v>0.012365936750454332</v>
+        <v>0.012361519714056015</v>
       </c>
     </row>
     <row r="31" spans="1:2">
       <c r="A31">
-        <v>0.050989311909198913</v>
+        <v>0.050978320293699045</v>
       </c>
       <c r="B31">
-        <v>0.01162759284035361</v>
+        <v>0.011623415196907348</v>
       </c>
     </row>
     <row r="32" spans="1:2">
       <c r="A32">
-        <v>0.052688955639505548</v>
+        <v>0.052677597636822344</v>
       </c>
       <c r="B32">
-        <v>0.010838090260538258</v>
+        <v>0.010834171378489695</v>
       </c>
     </row>
     <row r="33" spans="1:2">
       <c r="A33">
-        <v>0.054388599369812177</v>
+        <v>0.054376874979945644</v>
       </c>
       <c r="B33">
-        <v>0.0099570815806846059</v>
+        <v>0.00995345710845983</v>
       </c>
     </row>
     <row r="34" spans="1:2">
       <c r="A34">
-        <v>0.056088243100118812</v>
+        <v>0.056076152323068951</v>
       </c>
       <c r="B34">
-        <v>0.0090085933345202557</v>
+        <v>0.0090052907338736832</v>
       </c>
     </row>
     <row r="35" spans="1:2">
       <c r="A35">
-        <v>0.05778788683042544</v>
+        <v>0.05777542966619225</v>
       </c>
       <c r="B35">
-        <v>0.0080055279931044235</v>
+        <v>0.0080025697394905653</v>
       </c>
     </row>
     <row r="36" spans="1:2">
       <c r="A36">
-        <v>0.059487530560732069</v>
+        <v>0.05947470700931555</v>
       </c>
       <c r="B36">
-        <v>0.0068974396345324821</v>
+        <v>0.0068948707003450042</v>
       </c>
     </row>
     <row r="37" spans="1:2">
       <c r="A37">
-        <v>0.0611871742910387</v>
+        <v>0.06117398435243885</v>
       </c>
       <c r="B37">
-        <v>0.005714583327294926</v>
+        <v>0.0057124376831210388</v>
       </c>
     </row>
     <row r="38" spans="1:2">
       <c r="A38">
-        <v>0.062886818021345325</v>
+        <v>0.062873261695562149</v>
       </c>
       <c r="B38">
-        <v>0.0044705388344550767</v>
+        <v>0.0044688445619296422</v>
       </c>
     </row>
     <row r="39" spans="1:2">
       <c r="A39">
-        <v>0.064586461751651961</v>
+        <v>0.064572539038685456</v>
       </c>
       <c r="B39">
-        <v>0.003095466696559579</v>
+        <v>0.0030942875806971555</v>
       </c>
     </row>
     <row r="40" spans="1:2">
       <c r="A40">
-        <v>0.0662861054819586</v>
+        <v>0.066271816381808762</v>
       </c>
       <c r="B40">
-        <v>0.0017203945586640817</v>
+        <v>0.0017197305994646685</v>
       </c>
     </row>
     <row r="41" spans="1:2">
       <c r="A41">
-        <v>0.067985749212265217</v>
+        <v>0.067971093724932055</v>
       </c>
       <c r="B41">
-        <v>0.0003453224207685899</v>
+        <v>0.00034517361823218696</v>
       </c>
     </row>
     <row r="42" spans="1:2">
       <c r="A42">
-        <v>0.067985749212265217</v>
+        <v>0.067971093724932055</v>
       </c>
       <c r="B42">
-        <v>9.1060514363934392E-05</v>
+        <v>9.0966522316373092E-05</v>
       </c>
     </row>
     <row r="43" spans="1:2">
       <c r="A43">
-        <v>0.0662861054819586</v>
+        <v>0.066271816381808762</v>
       </c>
       <c r="B43">
-        <v>0.00090988924159719959</v>
+        <v>0.000909400000637202</v>
       </c>
     </row>
     <row r="44" spans="1:2">
       <c r="A44">
-        <v>0.064586461751651961</v>
+        <v>0.064572539038685456</v>
       </c>
       <c r="B44">
-        <v>0.0017287179688304686</v>
+        <v>0.0017278334789580347</v>
       </c>
     </row>
     <row r="45" spans="1:2">
       <c r="A45">
-        <v>0.062886818021345325</v>
+        <v>0.062873261695562149</v>
       </c>
       <c r="B45">
-        <v>0.0025475466960637378</v>
+        <v>0.0025462669572788674</v>
       </c>
     </row>
     <row r="46" spans="1:2">
       <c r="A46">
-        <v>0.0611871742910387</v>
+        <v>0.06117398435243885</v>
       </c>
       <c r="B46">
-        <v>0.003258239048184881</v>
+        <v>0.0032566229108986211</v>
       </c>
     </row>
     <row r="47" spans="1:2">
       <c r="A47">
-        <v>0.059487530560732069</v>
+        <v>0.05947470700931555</v>
       </c>
       <c r="B47">
-        <v>0.0039187487209285153</v>
+        <v>0.0039168218943512285</v>
       </c>
     </row>
     <row r="48" spans="1:2">
       <c r="A48">
-        <v>0.05778788683042544</v>
+        <v>0.05777542966619225</v>
       </c>
       <c r="B48">
-        <v>0.0045180019947245213</v>
+        <v>0.0045157955367985184</v>
       </c>
     </row>
     <row r="49" spans="1:2">
       <c r="A49">
-        <v>0.056088243100118812</v>
+        <v>0.056076152323068951</v>
       </c>
       <c r="B49">
-        <v>0.0050318904571119965</v>
+        <v>0.0050294451025695392</v>
       </c>
     </row>
     <row r="50" spans="1:2">
       <c r="A50">
-        <v>0.054388599369812177</v>
+        <v>0.054376874979945644</v>
       </c>
       <c r="B50">
-        <v>0.0055017406570293656</v>
+        <v>0.0054990766094998849</v>
       </c>
     </row>
     <row r="51" spans="1:2">
       <c r="A51">
-        <v>0.052688955639505548</v>
+        <v>0.052677597636822344</v>
       </c>
       <c r="B51">
-        <v>0.0059172596314066069</v>
+        <v>0.0059144015182954974</v>
       </c>
     </row>
     <row r="52" spans="1:2">
       <c r="A52">
-        <v>0.050989311909198913</v>
+        <v>0.050978320293699045</v>
       </c>
       <c r="B52">
-        <v>0.0062599724461748132</v>
+        <v>0.0062569518848171893</v>
       </c>
     </row>
     <row r="53" spans="1:2">
       <c r="A53">
-        <v>0.049289668178892292</v>
+        <v>0.049279042950575745</v>
       </c>
       <c r="B53">
-        <v>0.0065624477108060424</v>
+        <v>0.0065592817154140268</v>
       </c>
     </row>
     <row r="54" spans="1:2">
       <c r="A54">
-        <v>0.047590024448585656</v>
+        <v>0.047579765607452446</v>
       </c>
       <c r="B54">
-        <v>0.0068187803647302737</v>
+        <v>0.0068154882861921487</v>
       </c>
     </row>
     <row r="55" spans="1:2">
       <c r="A55">
-        <v>0.045890380718279028</v>
+        <v>0.045880488264329139</v>
       </c>
       <c r="B55">
-        <v>0.0070076250899541656</v>
+        <v>0.0070042344652511386</v>
       </c>
     </row>
     <row r="56" spans="1:2">
       <c r="A56">
-        <v>0.044190736987972393</v>
+        <v>0.044181210921205839</v>
       </c>
       <c r="B56">
-        <v>0.0071586667803055877</v>
+        <v>0.0071551927648715171</v>
       </c>
     </row>
     <row r="57" spans="1:2">
       <c r="A57">
-        <v>0.042491093257665757</v>
+        <v>0.042481933578082533</v>
       </c>
       <c r="B57">
-        <v>0.0072709947780857966</v>
+        <v>0.0072674528340661475</v>
       </c>
     </row>
     <row r="58" spans="1:2">
       <c r="A58">
-        <v>0.040791449527359136</v>
+        <v>0.04078265623495924</v>
       </c>
       <c r="B58">
-        <v>0.0073215542658121363</v>
+        <v>0.0073179687582659494</v>
       </c>
     </row>
     <row r="59" spans="1:2">
       <c r="A59">
-        <v>0.039091805797052508</v>
+        <v>0.039083378891835933</v>
       </c>
       <c r="B59">
-        <v>0.0073329138721345026</v>
+        <v>0.0073293001570604276</v>
       </c>
     </row>
     <row r="60" spans="1:2">
       <c r="A60">
-        <v>0.037392162066745872</v>
+        <v>0.037384101548712634</v>
       </c>
       <c r="B60">
-        <v>0.0073072832302911893</v>
+        <v>0.0073036557952948821</v>
       </c>
     </row>
     <row r="61" spans="1:2">
       <c r="A61">
-        <v>0.035692518336439244</v>
+        <v>0.035684824205589327</v>
       </c>
       <c r="B61">
-        <v>0.0072379052422061321</v>
+        <v>0.0072342812163436682</v>
       </c>
     </row>
     <row r="62" spans="1:2">
       <c r="A62">
-        <v>0.033992874606132609</v>
+        <v>0.033985546862466028</v>
       </c>
       <c r="B62">
-        <v>0.0071190544189580329</v>
+        <v>0.0071154532872031934</v>
       </c>
     </row>
     <row r="63" spans="1:2">
       <c r="A63">
-        <v>0.03229323087582598</v>
+        <v>0.032286269519342728</v>
       </c>
       <c r="B63">
-        <v>0.0069646723715445337</v>
+        <v>0.0069611082709526585</v>
       </c>
     </row>
     <row r="64" spans="1:2">
       <c r="A64">
-        <v>0.030593587145519349</v>
+        <v>0.030586992176219425</v>
       </c>
       <c r="B64">
-        <v>0.0067741692015367361</v>
+        <v>0.0067706566304715481</v>
       </c>
     </row>
     <row r="65" spans="1:2">
       <c r="A65">
-        <v>0.02889394341521272</v>
+        <v>0.028887714833096125</v>
       </c>
       <c r="B65">
-        <v>0.0065464915274407037</v>
+        <v>0.0065430455869229642</v>
       </c>
     </row>
     <row r="66" spans="1:2">
       <c r="A66">
-        <v>0.027194299684906088</v>
+        <v>0.027188437489972822</v>
       </c>
       <c r="B66">
-        <v>0.0062719844864476508</v>
+        <v>0.0062686246870248073</v>
       </c>
     </row>
     <row r="67" spans="1:2">
       <c r="A67">
-        <v>0.025494655954599457</v>
+        <v>0.025489160146849522</v>
       </c>
       <c r="B67">
-        <v>0.0059631952951369879</v>
+        <v>0.0059599363793646342</v>
       </c>
     </row>
     <row r="68" spans="1:2">
       <c r="A68">
-        <v>0.023795012224292828</v>
+        <v>0.023789882803726223</v>
       </c>
       <c r="B68">
-        <v>0.0056199882406230747</v>
+        <v>0.0056168454220029973</v>
       </c>
     </row>
     <row r="69" spans="1:2">
       <c r="A69">
-        <v>0.022095368493986196</v>
+        <v>0.02209060546060292</v>
       </c>
       <c r="B69">
-        <v>0.0052424507504102271</v>
+        <v>0.0052394397329295767</v>
       </c>
     </row>
     <row r="70" spans="1:2">
       <c r="A70">
-        <v>0.020395724763679568</v>
+        <v>0.02039132811747962</v>
       </c>
       <c r="B70">
-        <v>0.0048309350270308981</v>
+        <v>0.0048280720316416295</v>
       </c>
     </row>
     <row r="71" spans="1:2">
       <c r="A71">
-        <v>0.018696081033372936</v>
+        <v>0.018692050774356317</v>
       </c>
       <c r="B71">
-        <v>0.0043861183644629074</v>
+        <v>0.0043834201562748271</v>
       </c>
     </row>
     <row r="72" spans="1:2">
       <c r="A72">
-        <v>0.016996437303066304</v>
+        <v>0.016992773431233014</v>
       </c>
       <c r="B72">
-        <v>0.0039090893332858548</v>
+        <v>0.00390657324107181</v>
       </c>
     </row>
     <row r="73" spans="1:2">
       <c r="A73">
-        <v>0.015296793572759674</v>
+        <v>0.015293496088109712</v>
       </c>
       <c r="B73">
-        <v>0.0034014704561000555</v>
+        <v>0.0033991543721980733</v>
       </c>
     </row>
     <row r="74" spans="1:2">
       <c r="A74">
-        <v>0.013597149842453044</v>
+        <v>0.013594218744986411</v>
       </c>
       <c r="B74">
-        <v>0.0028655927496587276</v>
+        <v>0.0028634950931694931</v>
       </c>
     </row>
     <row r="75" spans="1:2">
       <c r="A75">
-        <v>0.011897506112146414</v>
+        <v>0.011894941401863111</v>
       </c>
       <c r="B75">
-        <v>0.0023047444430675736</v>
+        <v>0.00230288406188016</v>
       </c>
     </row>
     <row r="76" spans="1:2">
       <c r="A76">
-        <v>0.010197862381839784</v>
+        <v>0.01019566405873981</v>
       </c>
       <c r="B76">
-        <v>0.0017235268139964841</v>
+        <v>0.0017219227908481466</v>
       </c>
     </row>
     <row r="77" spans="1:2">
       <c r="A77">
-        <v>0.0084982186515331522</v>
+        <v>0.0084963867156165069</v>
       </c>
       <c r="B77">
-        <v>0.0011283672214373482</v>
+        <v>0.0011270385346410616</v>
       </c>
     </row>
     <row r="78" spans="1:2">
       <c r="A78">
-        <v>0.0067985749212265221</v>
+        <v>0.0067971093724932055</v>
       </c>
       <c r="B78">
-        <v>0.00052933319444710251</v>
+        <v>0.00052830012614102492</v>
       </c>
     </row>
     <row r="79" spans="1:2">
       <c r="A79">
-        <v>0.005098931190919892</v>
+        <v>0.005097832029369905</v>
       </c>
       <c r="B79">
-        <v>-5.5105529771081816E-05</v>
+        <v>-5.5824830590906132E-05</v>
       </c>
     </row>
     <row r="80" spans="1:2">
       <c r="A80">
-        <v>0.003399287460613261</v>
+        <v>0.0033985546862466028</v>
       </c>
       <c r="B80">
-        <v>-0.00058362388142422291</v>
+        <v>-0.00058401622544583065</v>
       </c>
     </row>
     <row r="81" spans="1:2">
       <c r="A81">
-        <v>0.0016996437303066305</v>
+        <v>0.0016992773431233014</v>
       </c>
       <c r="B81">
-        <v>-0.00095239285724307225</v>
+        <v>-0.00095246403282174508</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -1663,7 +1663,7 @@
         <v>0</v>
       </c>
       <c r="B82">
-        <v>-7.5479344121848443E-18</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1681,647 +1681,647 @@
         <v>0</v>
       </c>
       <c r="B1">
-        <v>-7.5479344121848443E-18</v>
+        <v>0</v>
       </c>
     </row>
     <row r="2" spans="1:2">
       <c r="A2">
-        <v>0.0016996437303066305</v>
+        <v>0.0016992773431233014</v>
       </c>
       <c r="B2">
-        <v>0.0034819219694949238</v>
+        <v>0.0034808949017546219</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3">
-        <v>0.003399287460613261</v>
+        <v>0.0033985546862466028</v>
       </c>
       <c r="B3">
-        <v>0.0054474284540267943</v>
+        <v>0.005445736013850744</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4">
-        <v>0.005098931190919892</v>
+        <v>0.005097832029369905</v>
       </c>
       <c r="B4">
-        <v>0.0070768979818683665</v>
+        <v>0.0070746412560979306</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5">
-        <v>0.0067985749212265221</v>
+        <v>0.0067971093724932055</v>
       </c>
       <c r="B5">
-        <v>0.008481021406424951</v>
+        <v>0.008478274216156283</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6">
-        <v>0.0084982186515331522</v>
+        <v>0.0084963867156165069</v>
       </c>
       <c r="B6">
-        <v>0.0097149260966221049</v>
+        <v>0.00971174643066785</v>
       </c>
     </row>
     <row r="7" spans="1:2">
       <c r="A7">
-        <v>0.010197862381839784</v>
+        <v>0.01019566405873981</v>
       </c>
       <c r="B7">
-        <v>0.010799318011759323</v>
+        <v>0.010795757547084955</v>
       </c>
     </row>
     <row r="8" spans="1:2">
       <c r="A8">
-        <v>0.011897506112146414</v>
+        <v>0.011894941401863111</v>
       </c>
       <c r="B8">
-        <v>0.011762002167472066</v>
+        <v>0.011758103113145173</v>
       </c>
     </row>
     <row r="9" spans="1:2">
       <c r="A9">
-        <v>0.013597149842453044</v>
+        <v>0.013594218744986411</v>
       </c>
       <c r="B9">
-        <v>0.012611883884145053</v>
+        <v>0.01260768524843706</v>
       </c>
     </row>
     <row r="10" spans="1:2">
       <c r="A10">
-        <v>0.015296793572759674</v>
+        <v>0.015293496088109712</v>
       </c>
       <c r="B10">
-        <v>0.01335671996926893</v>
+        <v>0.013352257861607127</v>
       </c>
     </row>
     <row r="11" spans="1:2">
       <c r="A11">
-        <v>0.016996437303066304</v>
+        <v>0.016992773431233014</v>
       </c>
       <c r="B11">
-        <v>0.014003398151060229</v>
+        <v>0.013998706058482432</v>
       </c>
     </row>
     <row r="12" spans="1:2">
       <c r="A12">
-        <v>0.018696081033372936</v>
+        <v>0.018692050774356317</v>
       </c>
       <c r="B12">
-        <v>0.014558108410664874</v>
+        <v>0.014553217456599864</v>
       </c>
     </row>
     <row r="13" spans="1:2">
       <c r="A13">
-        <v>0.020395724763679568</v>
+        <v>0.02039132811747962</v>
       </c>
       <c r="B13">
-        <v>0.01502645121755068</v>
+        <v>0.015021390404822976</v>
       </c>
     </row>
     <row r="14" spans="1:2">
       <c r="A14">
-        <v>0.022095368493986196</v>
+        <v>0.02209060546060292</v>
       </c>
       <c r="B14">
-        <v>0.015413509988431271</v>
+        <v>0.015408306425725262</v>
       </c>
     </row>
     <row r="15" spans="1:2">
       <c r="A15">
-        <v>0.023795012224292828</v>
+        <v>0.023789882803726223</v>
       </c>
       <c r="B15">
-        <v>0.01572390460116365</v>
+        <v>0.015718583711110175</v>
       </c>
     </row>
     <row r="16" spans="1:2">
       <c r="A16">
-        <v>0.025494655954599457</v>
+        <v>0.025489160146849522</v>
       </c>
       <c r="B16">
-        <v>0.015961836466076323</v>
+        <v>0.015956422172732531</v>
       </c>
     </row>
     <row r="17" spans="1:2">
       <c r="A17">
-        <v>0.027194299684906088</v>
+        <v>0.027188437489972822</v>
       </c>
       <c r="B17">
-        <v>0.016131131800279724</v>
+        <v>0.016125646693564578</v>
       </c>
     </row>
     <row r="18" spans="1:2">
       <c r="A18">
-        <v>0.02889394341521272</v>
+        <v>0.028887714833096125</v>
       </c>
       <c r="B18">
-        <v>0.016235287406259191</v>
+        <v>0.016229752880605287</v>
       </c>
     </row>
     <row r="19" spans="1:2">
       <c r="A19">
-        <v>0.030593587145519349</v>
+        <v>0.030586992176219425</v>
       </c>
       <c r="B19">
-        <v>0.016255800823513359</v>
+        <v>0.016250244325099521</v>
       </c>
     </row>
     <row r="20" spans="1:2">
       <c r="A20">
-        <v>0.03229323087582598</v>
+        <v>0.032286269519342728</v>
       </c>
       <c r="B20">
-        <v>0.016213615467260578</v>
+        <v>0.016208057599299</v>
       </c>
     </row>
     <row r="21" spans="1:2">
       <c r="A21">
-        <v>0.033992874606132609</v>
+        <v>0.033985546862466028</v>
       </c>
       <c r="B21">
-        <v>0.016112495800351911</v>
+        <v>0.01610695597897794</v>
       </c>
     </row>
     <row r="22" spans="1:2">
       <c r="A22">
-        <v>0.035692518336439244</v>
+        <v>0.035684824205589327</v>
       </c>
       <c r="B22">
-        <v>0.015954931175805653</v>
+        <v>0.015949428046386445</v>
       </c>
     </row>
     <row r="23" spans="1:2">
       <c r="A23">
-        <v>0.037392162066745872</v>
+        <v>0.037384101548712634</v>
       </c>
       <c r="B23">
-        <v>0.015721789050567953</v>
+        <v>0.015716347725383</v>
       </c>
     </row>
     <row r="24" spans="1:2">
       <c r="A24">
-        <v>0.039091805797052508</v>
+        <v>0.039083378891835933</v>
       </c>
       <c r="B24">
-        <v>0.015424561170689136</v>
+        <v>0.015419203163085192</v>
       </c>
     </row>
     <row r="25" spans="1:2">
       <c r="A25">
-        <v>0.040791449527359136</v>
+        <v>0.04078265623495924</v>
       </c>
       <c r="B25">
-        <v>0.01507433352262233</v>
+        <v>0.015069076771330041</v>
       </c>
     </row>
     <row r="26" spans="1:2">
       <c r="A26">
-        <v>0.042491093257665757</v>
+        <v>0.042481933578082533</v>
       </c>
       <c r="B26">
-        <v>0.014668767825262144</v>
+        <v>0.01466363116513739</v>
       </c>
     </row>
     <row r="27" spans="1:2">
       <c r="A27">
-        <v>0.044190736987972393</v>
+        <v>0.044181210921205839</v>
       </c>
       <c r="B27">
-        <v>0.014178762307020913</v>
+        <v>0.014173774990310303</v>
       </c>
     </row>
     <row r="28" spans="1:2">
       <c r="A28">
-        <v>0.045890380718279028</v>
+        <v>0.045880488264329139</v>
       </c>
       <c r="B28">
-        <v>0.013637151349257243</v>
+        <v>0.013632331617142092</v>
       </c>
     </row>
     <row r="29" spans="1:2">
       <c r="A29">
-        <v>0.047590024448585656</v>
+        <v>0.047579765607452446</v>
       </c>
       <c r="B29">
-        <v>0.013045409806481747</v>
+        <v>0.013040775471809516</v>
       </c>
     </row>
     <row r="30" spans="1:2">
       <c r="A30">
-        <v>0.049289668178892292</v>
+        <v>0.049279042950575745</v>
       </c>
       <c r="B30">
-        <v>0.012365936750454332</v>
+        <v>0.012361519714056015</v>
       </c>
     </row>
     <row r="31" spans="1:2">
       <c r="A31">
-        <v>0.050989311909198913</v>
+        <v>0.050978320293699045</v>
       </c>
       <c r="B31">
-        <v>0.01162759284035361</v>
+        <v>0.011623415196907348</v>
       </c>
     </row>
     <row r="32" spans="1:2">
       <c r="A32">
-        <v>0.052688955639505548</v>
+        <v>0.052677597636822344</v>
       </c>
       <c r="B32">
-        <v>0.010838090260538258</v>
+        <v>0.010834171378489695</v>
       </c>
     </row>
     <row r="33" spans="1:2">
       <c r="A33">
-        <v>0.054388599369812177</v>
+        <v>0.054376874979945644</v>
       </c>
       <c r="B33">
-        <v>0.0099570815806846059</v>
+        <v>0.00995345710845983</v>
       </c>
     </row>
     <row r="34" spans="1:2">
       <c r="A34">
-        <v>0.056088243100118812</v>
+        <v>0.056076152323068951</v>
       </c>
       <c r="B34">
-        <v>0.0090085933345202557</v>
+        <v>0.0090052907338736832</v>
       </c>
     </row>
     <row r="35" spans="1:2">
       <c r="A35">
-        <v>0.05778788683042544</v>
+        <v>0.05777542966619225</v>
       </c>
       <c r="B35">
-        <v>0.0080055279931044235</v>
+        <v>0.0080025697394905653</v>
       </c>
     </row>
     <row r="36" spans="1:2">
       <c r="A36">
-        <v>0.059487530560732069</v>
+        <v>0.05947470700931555</v>
       </c>
       <c r="B36">
-        <v>0.0068974396345324821</v>
+        <v>0.0068948707003450042</v>
       </c>
     </row>
     <row r="37" spans="1:2">
       <c r="A37">
-        <v>0.0611871742910387</v>
+        <v>0.06117398435243885</v>
       </c>
       <c r="B37">
-        <v>0.005714583327294926</v>
+        <v>0.0057124376831210388</v>
       </c>
     </row>
     <row r="38" spans="1:2">
       <c r="A38">
-        <v>0.062886818021345325</v>
+        <v>0.062873261695562149</v>
       </c>
       <c r="B38">
-        <v>0.0044705388344550767</v>
+        <v>0.0044688445619296422</v>
       </c>
     </row>
     <row r="39" spans="1:2">
       <c r="A39">
-        <v>0.064586461751651961</v>
+        <v>0.064572539038685456</v>
       </c>
       <c r="B39">
-        <v>0.003095466696559579</v>
+        <v>0.0030942875806971555</v>
       </c>
     </row>
     <row r="40" spans="1:2">
       <c r="A40">
-        <v>0.0662861054819586</v>
+        <v>0.066271816381808762</v>
       </c>
       <c r="B40">
-        <v>0.0017203945586640817</v>
+        <v>0.0017197305994646685</v>
       </c>
     </row>
     <row r="41" spans="1:2">
       <c r="A41">
-        <v>0.067985749212265217</v>
+        <v>0.067971093724932055</v>
       </c>
       <c r="B41">
-        <v>0.0003453224207685899</v>
+        <v>0.00034517361823218696</v>
       </c>
     </row>
     <row r="42" spans="1:2">
       <c r="A42">
-        <v>0.067985749212265217</v>
+        <v>0.067971093724932055</v>
       </c>
       <c r="B42">
-        <v>9.1060514363934392E-05</v>
+        <v>9.0966522316373092E-05</v>
       </c>
     </row>
     <row r="43" spans="1:2">
       <c r="A43">
-        <v>0.0662861054819586</v>
+        <v>0.066271816381808762</v>
       </c>
       <c r="B43">
-        <v>0.00090988924159719959</v>
+        <v>0.000909400000637202</v>
       </c>
     </row>
     <row r="44" spans="1:2">
       <c r="A44">
-        <v>0.064586461751651961</v>
+        <v>0.064572539038685456</v>
       </c>
       <c r="B44">
-        <v>0.0017287179688304686</v>
+        <v>0.0017278334789580347</v>
       </c>
     </row>
     <row r="45" spans="1:2">
       <c r="A45">
-        <v>0.062886818021345325</v>
+        <v>0.062873261695562149</v>
       </c>
       <c r="B45">
-        <v>0.0025475466960637378</v>
+        <v>0.0025462669572788674</v>
       </c>
     </row>
     <row r="46" spans="1:2">
       <c r="A46">
-        <v>0.0611871742910387</v>
+        <v>0.06117398435243885</v>
       </c>
       <c r="B46">
-        <v>0.003258239048184881</v>
+        <v>0.0032566229108986211</v>
       </c>
     </row>
     <row r="47" spans="1:2">
       <c r="A47">
-        <v>0.059487530560732069</v>
+        <v>0.05947470700931555</v>
       </c>
       <c r="B47">
-        <v>0.0039187487209285153</v>
+        <v>0.0039168218943512285</v>
       </c>
     </row>
     <row r="48" spans="1:2">
       <c r="A48">
-        <v>0.05778788683042544</v>
+        <v>0.05777542966619225</v>
       </c>
       <c r="B48">
-        <v>0.0045180019947245213</v>
+        <v>0.0045157955367985184</v>
       </c>
     </row>
     <row r="49" spans="1:2">
       <c r="A49">
-        <v>0.056088243100118812</v>
+        <v>0.056076152323068951</v>
       </c>
       <c r="B49">
-        <v>0.0050318904571119965</v>
+        <v>0.0050294451025695392</v>
       </c>
     </row>
     <row r="50" spans="1:2">
       <c r="A50">
-        <v>0.054388599369812177</v>
+        <v>0.054376874979945644</v>
       </c>
       <c r="B50">
-        <v>0.0055017406570293656</v>
+        <v>0.0054990766094998849</v>
       </c>
     </row>
     <row r="51" spans="1:2">
       <c r="A51">
-        <v>0.052688955639505548</v>
+        <v>0.052677597636822344</v>
       </c>
       <c r="B51">
-        <v>0.0059172596314066069</v>
+        <v>0.0059144015182954974</v>
       </c>
     </row>
     <row r="52" spans="1:2">
       <c r="A52">
-        <v>0.050989311909198913</v>
+        <v>0.050978320293699045</v>
       </c>
       <c r="B52">
-        <v>0.0062599724461748132</v>
+        <v>0.0062569518848171893</v>
       </c>
     </row>
     <row r="53" spans="1:2">
       <c r="A53">
-        <v>0.049289668178892292</v>
+        <v>0.049279042950575745</v>
       </c>
       <c r="B53">
-        <v>0.0065624477108060424</v>
+        <v>0.0065592817154140268</v>
       </c>
     </row>
     <row r="54" spans="1:2">
       <c r="A54">
-        <v>0.047590024448585656</v>
+        <v>0.047579765607452446</v>
       </c>
       <c r="B54">
-        <v>0.0068187803647302737</v>
+        <v>0.0068154882861921487</v>
       </c>
     </row>
     <row r="55" spans="1:2">
       <c r="A55">
-        <v>0.045890380718279028</v>
+        <v>0.045880488264329139</v>
       </c>
       <c r="B55">
-        <v>0.0070076250899541656</v>
+        <v>0.0070042344652511386</v>
       </c>
     </row>
     <row r="56" spans="1:2">
       <c r="A56">
-        <v>0.044190736987972393</v>
+        <v>0.044181210921205839</v>
       </c>
       <c r="B56">
-        <v>0.0071586667803055877</v>
+        <v>0.0071551927648715171</v>
       </c>
     </row>
     <row r="57" spans="1:2">
       <c r="A57">
-        <v>0.042491093257665757</v>
+        <v>0.042481933578082533</v>
       </c>
       <c r="B57">
-        <v>0.0072709947780857966</v>
+        <v>0.0072674528340661475</v>
       </c>
     </row>
     <row r="58" spans="1:2">
       <c r="A58">
-        <v>0.040791449527359136</v>
+        <v>0.04078265623495924</v>
       </c>
       <c r="B58">
-        <v>0.0073215542658121363</v>
+        <v>0.0073179687582659494</v>
       </c>
     </row>
     <row r="59" spans="1:2">
       <c r="A59">
-        <v>0.039091805797052508</v>
+        <v>0.039083378891835933</v>
       </c>
       <c r="B59">
-        <v>0.0073329138721345026</v>
+        <v>0.0073293001570604276</v>
       </c>
     </row>
     <row r="60" spans="1:2">
       <c r="A60">
-        <v>0.037392162066745872</v>
+        <v>0.037384101548712634</v>
       </c>
       <c r="B60">
-        <v>0.0073072832302911893</v>
+        <v>0.0073036557952948821</v>
       </c>
     </row>
     <row r="61" spans="1:2">
       <c r="A61">
-        <v>0.035692518336439244</v>
+        <v>0.035684824205589327</v>
       </c>
       <c r="B61">
-        <v>0.0072379052422061321</v>
+        <v>0.0072342812163436682</v>
       </c>
     </row>
     <row r="62" spans="1:2">
       <c r="A62">
-        <v>0.033992874606132609</v>
+        <v>0.033985546862466028</v>
       </c>
       <c r="B62">
-        <v>0.0071190544189580329</v>
+        <v>0.0071154532872031934</v>
       </c>
     </row>
     <row r="63" spans="1:2">
       <c r="A63">
-        <v>0.03229323087582598</v>
+        <v>0.032286269519342728</v>
       </c>
       <c r="B63">
-        <v>0.0069646723715445337</v>
+        <v>0.0069611082709526585</v>
       </c>
     </row>
     <row r="64" spans="1:2">
       <c r="A64">
-        <v>0.030593587145519349</v>
+        <v>0.030586992176219425</v>
       </c>
       <c r="B64">
-        <v>0.0067741692015367361</v>
+        <v>0.0067706566304715481</v>
       </c>
     </row>
     <row r="65" spans="1:2">
       <c r="A65">
-        <v>0.02889394341521272</v>
+        <v>0.028887714833096125</v>
       </c>
       <c r="B65">
-        <v>0.0065464915274407037</v>
+        <v>0.0065430455869229642</v>
       </c>
     </row>
     <row r="66" spans="1:2">
       <c r="A66">
-        <v>0.027194299684906088</v>
+        <v>0.027188437489972822</v>
       </c>
       <c r="B66">
-        <v>0.0062719844864476508</v>
+        <v>0.0062686246870248073</v>
       </c>
     </row>
     <row r="67" spans="1:2">
       <c r="A67">
-        <v>0.025494655954599457</v>
+        <v>0.025489160146849522</v>
       </c>
       <c r="B67">
-        <v>0.0059631952951369879</v>
+        <v>0.0059599363793646342</v>
       </c>
     </row>
     <row r="68" spans="1:2">
       <c r="A68">
-        <v>0.023795012224292828</v>
+        <v>0.023789882803726223</v>
       </c>
       <c r="B68">
-        <v>0.0056199882406230747</v>
+        <v>0.0056168454220029973</v>
       </c>
     </row>
     <row r="69" spans="1:2">
       <c r="A69">
-        <v>0.022095368493986196</v>
+        <v>0.02209060546060292</v>
       </c>
       <c r="B69">
-        <v>0.0052424507504102271</v>
+        <v>0.0052394397329295767</v>
       </c>
     </row>
     <row r="70" spans="1:2">
       <c r="A70">
-        <v>0.020395724763679568</v>
+        <v>0.02039132811747962</v>
       </c>
       <c r="B70">
-        <v>0.0048309350270308981</v>
+        <v>0.0048280720316416295</v>
       </c>
     </row>
     <row r="71" spans="1:2">
       <c r="A71">
-        <v>0.018696081033372936</v>
+        <v>0.018692050774356317</v>
       </c>
       <c r="B71">
-        <v>0.0043861183644629074</v>
+        <v>0.0043834201562748271</v>
       </c>
     </row>
     <row r="72" spans="1:2">
       <c r="A72">
-        <v>0.016996437303066304</v>
+        <v>0.016992773431233014</v>
       </c>
       <c r="B72">
-        <v>0.0039090893332858548</v>
+        <v>0.00390657324107181</v>
       </c>
     </row>
     <row r="73" spans="1:2">
       <c r="A73">
-        <v>0.015296793572759674</v>
+        <v>0.015293496088109712</v>
       </c>
       <c r="B73">
-        <v>0.0034014704561000555</v>
+        <v>0.0033991543721980733</v>
       </c>
     </row>
     <row r="74" spans="1:2">
       <c r="A74">
-        <v>0.013597149842453044</v>
+        <v>0.013594218744986411</v>
       </c>
       <c r="B74">
-        <v>0.0028655927496587276</v>
+        <v>0.0028634950931694931</v>
       </c>
     </row>
     <row r="75" spans="1:2">
       <c r="A75">
-        <v>0.011897506112146414</v>
+        <v>0.011894941401863111</v>
       </c>
       <c r="B75">
-        <v>0.0023047444430675736</v>
+        <v>0.00230288406188016</v>
       </c>
     </row>
     <row r="76" spans="1:2">
       <c r="A76">
-        <v>0.010197862381839784</v>
+        <v>0.01019566405873981</v>
       </c>
       <c r="B76">
-        <v>0.0017235268139964841</v>
+        <v>0.0017219227908481466</v>
       </c>
     </row>
     <row r="77" spans="1:2">
       <c r="A77">
-        <v>0.0084982186515331522</v>
+        <v>0.0084963867156165069</v>
       </c>
       <c r="B77">
-        <v>0.0011283672214373482</v>
+        <v>0.0011270385346410616</v>
       </c>
     </row>
     <row r="78" spans="1:2">
       <c r="A78">
-        <v>0.0067985749212265221</v>
+        <v>0.0067971093724932055</v>
       </c>
       <c r="B78">
-        <v>0.00052933319444710251</v>
+        <v>0.00052830012614102492</v>
       </c>
     </row>
     <row r="79" spans="1:2">
       <c r="A79">
-        <v>0.005098931190919892</v>
+        <v>0.005097832029369905</v>
       </c>
       <c r="B79">
-        <v>-5.5105529771081816E-05</v>
+        <v>-5.5824830590906132E-05</v>
       </c>
     </row>
     <row r="80" spans="1:2">
       <c r="A80">
-        <v>0.003399287460613261</v>
+        <v>0.0033985546862466028</v>
       </c>
       <c r="B80">
-        <v>-0.00058362388142422291</v>
+        <v>-0.00058401622544583065</v>
       </c>
     </row>
     <row r="81" spans="1:2">
       <c r="A81">
-        <v>0.0016996437303066305</v>
+        <v>0.0016992773431233014</v>
       </c>
       <c r="B81">
-        <v>-0.00095239285724307225</v>
+        <v>-0.00095246403282174508</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -2329,7 +2329,7 @@
         <v>0</v>
       </c>
       <c r="B82">
-        <v>-7.5479344121848443E-18</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
